--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Gesammelte_Datenbanken/thermal_springs_alps_with_HF_estimates.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Gesammelte_Datenbanken/thermal_springs_alps_with_HF_estimates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\Gesammelte_Datenbanken\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94a36cc37384f3e2/SPEICHER/Hochschule/7. Semester/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Gesammelte_Datenbanken/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69B98BA-085F-4DF1-9DCB-B8927DBB9308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SHEET1" sheetId="1" r:id="rId1"/>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Gesammelte_Datenbanken/thermal_springs_alps_with_HF_estimates.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Gesammelte_Datenbanken/thermal_springs_alps_with_HF_estimates.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94a36cc37384f3e2/SPEICHER/Hochschule/7. Semester/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Gesammelte_Datenbanken/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69B98BA-085F-4DF1-9DCB-B8927DBB9308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{B69B98BA-085F-4DF1-9DCB-B8927DBB9308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D1BC3B7-3D15-48FF-8EA4-608EB0281AF3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SHEET1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SHEET1!$A$1:$DO$312</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -2748,6 +2751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:DO312"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2832,6 +2836,7 @@
     <col min="114" max="115" width="33.7109375" customWidth="1"/>
     <col min="116" max="116" width="29.7109375" customWidth="1"/>
     <col min="117" max="118" width="28.7109375" customWidth="1"/>
+    <col min="119" max="119" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="30" x14ac:dyDescent="0.25">
@@ -3193,7 +3198,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="2" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>20</v>
       </c>
@@ -3318,7 +3323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>31</v>
       </c>
@@ -3443,7 +3448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>32</v>
       </c>
@@ -3568,7 +3573,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>33</v>
       </c>
@@ -3693,7 +3698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>45</v>
       </c>
@@ -3905,7 +3910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>66</v>
       </c>
@@ -4135,7 +4140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>67</v>
       </c>
@@ -4341,7 +4346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>68</v>
       </c>
@@ -4580,7 +4585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>69</v>
       </c>
@@ -4816,7 +4821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>70</v>
       </c>
@@ -5022,7 +5027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>71</v>
       </c>
@@ -5228,7 +5233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>72</v>
       </c>
@@ -5440,7 +5445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>73</v>
       </c>
@@ -5679,7 +5684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>74</v>
       </c>
@@ -5915,7 +5920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>75</v>
       </c>
@@ -6145,7 +6150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>80</v>
       </c>
@@ -6351,7 +6356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>82</v>
       </c>
@@ -6485,7 +6490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>83</v>
       </c>
@@ -6691,7 +6696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>84</v>
       </c>
@@ -6939,7 +6944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>85</v>
       </c>
@@ -7142,7 +7147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>86</v>
       </c>
@@ -7345,7 +7350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>87</v>
       </c>
@@ -7548,7 +7553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>88</v>
       </c>
@@ -7751,7 +7756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>89</v>
       </c>
@@ -7954,7 +7959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>90</v>
       </c>
@@ -8157,7 +8162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>91</v>
       </c>
@@ -8360,7 +8365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>93</v>
       </c>
@@ -8563,7 +8568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>95</v>
       </c>
@@ -8766,7 +8771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>96</v>
       </c>
@@ -8969,7 +8974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>98</v>
       </c>
@@ -9172,7 +9177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>110</v>
       </c>
@@ -9420,7 +9425,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>133</v>
       </c>
@@ -9668,7 +9673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>138</v>
       </c>
@@ -9877,7 +9882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>139</v>
       </c>
@@ -10002,7 +10007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>140</v>
       </c>
@@ -10127,7 +10132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>142</v>
       </c>
@@ -10375,7 +10380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>143</v>
       </c>
@@ -10626,7 +10631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>144</v>
       </c>
@@ -10832,7 +10837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>150</v>
       </c>
@@ -11125,7 +11130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>151</v>
       </c>
@@ -11328,7 +11333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>152</v>
       </c>
@@ -11531,7 +11536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>153</v>
       </c>
@@ -11815,7 +11820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>154</v>
       </c>
@@ -12090,7 +12095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>156</v>
       </c>
@@ -12371,7 +12376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>157</v>
       </c>
@@ -12574,7 +12579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>158</v>
       </c>
@@ -12849,7 +12854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>159</v>
       </c>
@@ -13130,7 +13135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>160</v>
       </c>
@@ -13414,7 +13419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>161</v>
       </c>
@@ -13539,7 +13544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>162</v>
       </c>
@@ -13673,7 +13678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>168</v>
       </c>
@@ -13876,7 +13881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>169</v>
       </c>
@@ -14151,7 +14156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>170</v>
       </c>
@@ -14354,7 +14359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>180</v>
       </c>
@@ -14530,7 +14535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>200</v>
       </c>
@@ -14706,7 +14711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>201</v>
       </c>
@@ -14882,7 +14887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>203</v>
       </c>
@@ -15058,7 +15063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>212</v>
       </c>
@@ -15240,7 +15245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>216</v>
       </c>
@@ -15416,7 +15421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>218</v>
       </c>
@@ -15592,7 +15597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>219</v>
       </c>
@@ -15774,7 +15779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>222</v>
       </c>
@@ -15953,7 +15958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>227</v>
       </c>
@@ -16135,7 +16140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>229</v>
       </c>
@@ -16317,7 +16322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>243</v>
       </c>
@@ -16520,7 +16525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>245</v>
       </c>
@@ -16636,7 +16641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>247</v>
       </c>
@@ -16761,7 +16766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>248</v>
       </c>
@@ -16886,7 +16891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>249</v>
       </c>
@@ -17011,7 +17016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>250</v>
       </c>
@@ -17136,7 +17141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>251</v>
       </c>
@@ -17261,7 +17266,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>252</v>
       </c>
@@ -17389,7 +17394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>254</v>
       </c>
@@ -17514,7 +17519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>255</v>
       </c>
@@ -17639,7 +17644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>257</v>
       </c>
@@ -17764,7 +17769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>258</v>
       </c>
@@ -17970,7 +17975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>260</v>
       </c>
@@ -18095,7 +18100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>261</v>
       </c>
@@ -18220,7 +18225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>263</v>
       </c>
@@ -18345,7 +18350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>268</v>
       </c>
@@ -18470,7 +18475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>271</v>
       </c>
@@ -18646,7 +18651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>284</v>
       </c>
@@ -18894,7 +18899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>285</v>
       </c>
@@ -19139,7 +19144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>286</v>
       </c>
@@ -19384,7 +19389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>287</v>
       </c>
@@ -19623,7 +19628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>298</v>
       </c>
@@ -19874,7 +19879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>299</v>
       </c>
@@ -20023,7 +20028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>300</v>
       </c>
@@ -20268,7 +20273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>301</v>
       </c>
@@ -20519,7 +20524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>302</v>
       </c>
@@ -20767,7 +20772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>306</v>
       </c>
@@ -21018,7 +21023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>307</v>
       </c>
@@ -21269,7 +21274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>310</v>
       </c>
@@ -21508,7 +21513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>313</v>
       </c>
@@ -21741,7 +21746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>314</v>
       </c>
@@ -21983,7 +21988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>316</v>
       </c>
@@ -22234,7 +22239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>317</v>
       </c>
@@ -22485,7 +22490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>318</v>
       </c>
@@ -22736,7 +22741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>319</v>
       </c>
@@ -22987,7 +22992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>320</v>
       </c>
@@ -23241,7 +23246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>321</v>
       </c>
@@ -23492,7 +23497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>328</v>
       </c>
@@ -23737,7 +23742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>329</v>
       </c>
@@ -23928,7 +23933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>334</v>
       </c>
@@ -24173,7 +24178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>335</v>
       </c>
@@ -24415,7 +24420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>336</v>
       </c>
@@ -24669,7 +24674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>341</v>
       </c>
@@ -24908,7 +24913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>342</v>
       </c>
@@ -25159,7 +25164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>343</v>
       </c>
@@ -25410,7 +25415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>344</v>
       </c>
@@ -25652,7 +25657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>345</v>
       </c>
@@ -25945,7 +25950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>348</v>
       </c>
@@ -26196,7 +26201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>349</v>
       </c>
@@ -26447,7 +26452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>352</v>
       </c>
@@ -26575,7 +26580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>353</v>
       </c>
@@ -26703,7 +26708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>357</v>
       </c>
@@ -26993,7 +26998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>358</v>
       </c>
@@ -27277,7 +27282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>359</v>
       </c>
@@ -27435,7 +27440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>360</v>
       </c>
@@ -27590,7 +27595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>361</v>
       </c>
@@ -27751,7 +27756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>362</v>
       </c>
@@ -27906,7 +27911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>363</v>
       </c>
@@ -28058,7 +28063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>364</v>
       </c>
@@ -28213,7 +28218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>390</v>
       </c>
@@ -28452,7 +28457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>395</v>
       </c>
@@ -28691,7 +28696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>401</v>
       </c>
@@ -28936,7 +28941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>407</v>
       </c>
@@ -29157,7 +29162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>408</v>
       </c>
@@ -29300,7 +29305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>409</v>
       </c>
@@ -29443,7 +29448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>410</v>
       </c>
@@ -29670,7 +29675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>411</v>
       </c>
@@ -29900,7 +29905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>412</v>
       </c>
@@ -30130,7 +30135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>413</v>
       </c>
@@ -30354,7 +30359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>414</v>
       </c>
@@ -30578,7 +30583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>415</v>
       </c>
@@ -30802,7 +30807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>416</v>
       </c>
@@ -31026,7 +31031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>417</v>
       </c>
@@ -31172,7 +31177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>418</v>
       </c>
@@ -31396,7 +31401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>419</v>
       </c>
@@ -31584,7 +31589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>420</v>
       </c>
@@ -31775,7 +31780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>421</v>
       </c>
@@ -31957,7 +31962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>423</v>
       </c>
@@ -32238,7 +32243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>424</v>
       </c>
@@ -32519,7 +32524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>425</v>
       </c>
@@ -32746,7 +32751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>426</v>
       </c>
@@ -32955,7 +32960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>428</v>
       </c>
@@ -33230,7 +33235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>429</v>
       </c>
@@ -33430,7 +33435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>430</v>
       </c>
@@ -33708,7 +33713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>431</v>
       </c>
@@ -33986,7 +33991,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>432</v>
       </c>
@@ -34264,7 +34269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>433</v>
       </c>
@@ -34542,7 +34547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>436</v>
       </c>
@@ -34763,7 +34768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>437</v>
       </c>
@@ -34924,7 +34929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>438</v>
       </c>
@@ -35070,7 +35075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>440</v>
       </c>
@@ -35285,7 +35290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>442</v>
       </c>
@@ -35449,7 +35454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>444</v>
       </c>
@@ -35616,7 +35621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>450</v>
       </c>
@@ -35840,7 +35845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>452</v>
       </c>
@@ -36112,7 +36117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>453</v>
       </c>
@@ -36387,7 +36392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>454</v>
       </c>
@@ -36614,7 +36619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>455</v>
       </c>
@@ -36835,7 +36840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>457</v>
       </c>
@@ -37053,7 +37058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>460</v>
       </c>
@@ -37277,7 +37282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>461</v>
       </c>
@@ -37495,7 +37500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>464</v>
       </c>
@@ -37722,7 +37727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>465</v>
       </c>
@@ -38009,7 +38014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>466</v>
       </c>
@@ -38254,7 +38259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>467</v>
       </c>
@@ -38475,7 +38480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>468</v>
       </c>
@@ -38705,7 +38710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>469</v>
       </c>
@@ -38929,7 +38934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>470</v>
       </c>
@@ -39150,7 +39155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>473</v>
       </c>
@@ -39368,7 +39373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>474</v>
       </c>
@@ -39586,7 +39591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>475</v>
       </c>
@@ -39825,7 +39830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>476</v>
       </c>
@@ -39980,7 +39985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>477</v>
       </c>
@@ -40216,7 +40221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>478</v>
       </c>
@@ -40434,7 +40439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>479</v>
       </c>
@@ -40622,7 +40627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>480</v>
       </c>
@@ -40807,7 +40812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>481</v>
       </c>
@@ -41028,7 +41033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>482</v>
       </c>
@@ -41246,7 +41251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>485</v>
       </c>
@@ -41470,7 +41475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>489</v>
       </c>
@@ -41625,7 +41630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>504</v>
       </c>
@@ -41798,7 +41803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>505</v>
       </c>
@@ -41986,7 +41991,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>506</v>
       </c>
@@ -42180,7 +42185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>507</v>
       </c>
@@ -42374,7 +42379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>508</v>
       </c>
@@ -42619,7 +42624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>518</v>
       </c>
@@ -42753,7 +42758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>565</v>
       </c>
@@ -42992,7 +42997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>566</v>
       </c>
@@ -43231,7 +43236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>567</v>
       </c>
@@ -43473,7 +43478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>572</v>
       </c>
@@ -43763,7 +43768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>581</v>
       </c>
@@ -43999,7 +44004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>583</v>
       </c>
@@ -44232,7 +44237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>600</v>
       </c>
@@ -44420,7 +44425,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>601</v>
       </c>
@@ -44575,7 +44580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>615</v>
       </c>
@@ -44856,7 +44861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>619</v>
       </c>
@@ -45092,7 +45097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>623</v>
       </c>
@@ -45370,7 +45375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>624</v>
       </c>
@@ -45651,7 +45656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>632</v>
       </c>
@@ -45947,7 +45952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>643</v>
       </c>
@@ -46222,7 +46227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>644</v>
       </c>
@@ -46497,7 +46502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>645</v>
       </c>
@@ -46727,7 +46732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>646</v>
       </c>
@@ -46960,7 +46965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>650</v>
       </c>
@@ -47235,7 +47240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>651</v>
       </c>
@@ -47399,7 +47404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>652</v>
       </c>
@@ -47566,7 +47571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>655</v>
       </c>
@@ -47730,7 +47735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>656</v>
       </c>
@@ -47888,7 +47893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>657</v>
       </c>
@@ -48046,7 +48051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>658</v>
       </c>
@@ -48234,7 +48239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>659</v>
       </c>
@@ -48425,7 +48430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>660</v>
       </c>
@@ -48577,7 +48582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>662</v>
       </c>
@@ -48846,7 +48851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>663</v>
       </c>
@@ -49028,7 +49033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>665</v>
       </c>
@@ -49306,7 +49311,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>667</v>
       </c>
@@ -49584,7 +49589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>668</v>
       </c>
@@ -49826,7 +49831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>669</v>
       </c>
@@ -50065,7 +50070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>670</v>
       </c>
@@ -50241,7 +50246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>671</v>
       </c>
@@ -50516,7 +50521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>673</v>
       </c>
@@ -50791,7 +50796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>675</v>
       </c>
@@ -50982,7 +50987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>676</v>
       </c>
@@ -51269,7 +51274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>677</v>
       </c>
@@ -51556,7 +51561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>681</v>
       </c>
@@ -51846,7 +51851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>692</v>
       </c>
@@ -52085,7 +52090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>693</v>
       </c>
@@ -52243,7 +52248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>709</v>
       </c>
@@ -52473,7 +52478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>711</v>
       </c>
@@ -52715,7 +52720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>712</v>
       </c>
@@ -52954,7 +52959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>713</v>
       </c>
@@ -53229,7 +53234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>715</v>
       </c>
@@ -53474,7 +53479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>716</v>
       </c>
@@ -53749,7 +53754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>718</v>
       </c>
@@ -53928,7 +53933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>719</v>
       </c>
@@ -54170,7 +54175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>720</v>
       </c>
@@ -54415,7 +54420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>721</v>
       </c>
@@ -54657,7 +54662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>722</v>
       </c>
@@ -54899,7 +54904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>723</v>
       </c>
@@ -55057,7 +55062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>724</v>
       </c>
@@ -55347,7 +55352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>725</v>
       </c>
@@ -55472,7 +55477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>729</v>
       </c>
@@ -55681,7 +55686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>732</v>
       </c>
@@ -55884,7 +55889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>734</v>
       </c>
@@ -56024,7 +56029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>735</v>
       </c>
@@ -56233,7 +56238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>737</v>
       </c>
@@ -56376,7 +56381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>739</v>
       </c>
@@ -56504,7 +56509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>741</v>
       </c>
@@ -56638,7 +56643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>743</v>
       </c>
@@ -56847,7 +56852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>744</v>
       </c>
@@ -57050,7 +57055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>751</v>
       </c>
@@ -57304,7 +57309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>752</v>
       </c>
@@ -57555,7 +57560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>753</v>
       </c>
@@ -57803,7 +57808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>759</v>
       </c>
@@ -58045,7 +58050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>760</v>
       </c>
@@ -58254,7 +58259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>761</v>
       </c>
@@ -58385,7 +58390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>772</v>
       </c>
@@ -58669,7 +58674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>774</v>
       </c>
@@ -58941,7 +58946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>775</v>
       </c>
@@ -59081,7 +59086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>787</v>
       </c>
@@ -59359,7 +59364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>788</v>
       </c>
@@ -59634,7 +59639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>792</v>
       </c>
@@ -59837,7 +59842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>793</v>
       </c>
@@ -60130,7 +60135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>797</v>
       </c>
@@ -60405,7 +60410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>798</v>
       </c>
@@ -60608,7 +60613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>799</v>
       </c>
@@ -60823,7 +60828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>800</v>
       </c>
@@ -61101,7 +61106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>801</v>
       </c>
@@ -61301,7 +61306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>809</v>
       </c>
@@ -61570,7 +61575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>812</v>
       </c>
@@ -61836,7 +61841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>813</v>
       </c>
@@ -62039,7 +62044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>814</v>
       </c>
@@ -62317,7 +62322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>815</v>
       </c>
@@ -62604,7 +62609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>816</v>
       </c>
@@ -62882,7 +62887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>817</v>
       </c>
@@ -63160,7 +63165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>824</v>
       </c>
@@ -63327,7 +63332,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>825</v>
       </c>
@@ -63497,7 +63502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>826</v>
       </c>
@@ -63667,7 +63672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>828</v>
       </c>
@@ -63867,7 +63872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>831</v>
       </c>
@@ -64073,7 +64078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>832</v>
       </c>
@@ -64198,7 +64203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>833</v>
       </c>
@@ -64476,7 +64481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>834</v>
       </c>
@@ -64748,7 +64753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>836</v>
       </c>
@@ -64873,7 +64878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>839</v>
       </c>
@@ -65160,7 +65165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>840</v>
       </c>
@@ -65339,7 +65344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>842</v>
       </c>
@@ -65512,7 +65517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>845</v>
       </c>
@@ -65742,7 +65747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>849</v>
       </c>
@@ -65966,7 +65971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>856</v>
       </c>
@@ -66121,7 +66126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>870</v>
       </c>
@@ -66393,7 +66398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>886</v>
       </c>
@@ -66554,7 +66559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>887</v>
       </c>
@@ -66730,7 +66735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>891</v>
       </c>
@@ -66909,7 +66914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>906</v>
       </c>
@@ -67079,7 +67084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>913</v>
       </c>
@@ -67234,7 +67239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>931</v>
       </c>
@@ -67506,7 +67511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>934</v>
       </c>
@@ -67730,7 +67735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>935</v>
       </c>
@@ -67954,7 +67959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="305" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>936</v>
       </c>
@@ -68178,7 +68183,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="306" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>937</v>
       </c>
@@ -68402,7 +68407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>941</v>
       </c>
@@ -68626,7 +68631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="308" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>942</v>
       </c>
@@ -68847,7 +68852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>943</v>
       </c>
@@ -69071,7 +69076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>944</v>
       </c>
@@ -69295,7 +69300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:119" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>945</v>
       </c>
@@ -69649,8 +69654,16 @@
       <c r="CM312">
         <v>1057.754333496094</v>
       </c>
+      <c r="DO312">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:DO312" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="118">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>